--- a/results/Int All Data -0.6/Linea_fi_explain.xlsx
+++ b/results/Int All Data -0.6/Linea_fi_explain.xlsx
@@ -1760,7 +1760,7 @@
         <v>0.003480428441418658</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.003105555695443587</v>
+        <v>-0.003102601485694695</v>
       </c>
       <c r="AE3" t="n">
         <v>0.006519112880188996</v>
@@ -1778,7 +1778,7 @@
         <v>-0.0009707728312393939</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.01992758790676375</v>
+        <v>0.01993054736222395</v>
       </c>
       <c r="AK3" t="n">
         <v>0.0256292798622887</v>
@@ -1883,7 +1883,7 @@
         <v>0.00696697792528019</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.003488263166685385</v>
+        <v>0.003491212149286388</v>
       </c>
       <c r="BT3" t="n">
         <v>-0.00123911482743192</v>
@@ -1892,7 +1892,7 @@
         <v>0.001855847269032266</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0007511228243384239</v>
+        <v>0.000754256638189881</v>
       </c>
       <c r="BW3" t="n">
         <v>0.0001837026616162607</v>
@@ -1901,10 +1901,10 @@
         <v>0.007752233825545652</v>
       </c>
       <c r="BY3" t="n">
+        <v>0.0002561656591130668</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>0.000259125114573262</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0.0002561656591130668</v>
       </c>
       <c r="CA3" t="n">
         <v>0.009726126393306616</v>
@@ -1922,7 +1922,7 @@
         <v>0.001127930687359982</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.00112557889534341</v>
+        <v>0.001122522660624583</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4057770904990224</v>
@@ -2054,7 +2054,7 @@
         <v>0.0008726076908069204</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.006728603734523107</v>
+        <v>0.006731484748640078</v>
       </c>
       <c r="DY3" t="n">
         <v>0.009739229838522264</v>
@@ -2229,7 +2229,7 @@
         <v>0.007954411899760636</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004544230710298753</v>
+        <v>0.004546845578882306</v>
       </c>
       <c r="AE4" t="n">
         <v>0.004273274246699023</v>
@@ -2247,7 +2247,7 @@
         <v>0.001696544224376826</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.01647602020773921</v>
+        <v>0.01647886155174322</v>
       </c>
       <c r="AK4" t="n">
         <v>0.01375895736560777</v>
@@ -2352,7 +2352,7 @@
         <v>0.01619114430883199</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.01001663547147019</v>
+        <v>0.01001465926962477</v>
       </c>
       <c r="BT4" t="n">
         <v>0.001271287896368118</v>
@@ -2361,7 +2361,7 @@
         <v>0.01180571118940769</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.008356134453116641</v>
+        <v>0.008359300337975365</v>
       </c>
       <c r="BW4" t="n">
         <v>0.0003542852219701615</v>
@@ -2370,10 +2370,10 @@
         <v>0.0152469769168383</v>
       </c>
       <c r="BY4" t="n">
+        <v>0.002158830530807663</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>0.002158280248566059</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.002158830530807663</v>
       </c>
       <c r="CA4" t="n">
         <v>0.01645424058585193</v>
@@ -2391,7 +2391,7 @@
         <v>0.004344552135893899</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002277341899628543</v>
+        <v>0.002279176771701213</v>
       </c>
       <c r="CG4" t="n">
         <v>0.08246576340760917</v>
@@ -2523,7 +2523,7 @@
         <v>0.003501163665459609</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.01073924082670948</v>
+        <v>0.0107384842289019</v>
       </c>
       <c r="DY4" t="n">
         <v>0.02848587163961338</v>
@@ -3329,7 +3329,7 @@
         <v>-0.0002907301939516632</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0001556259774362911</v>
+        <v>-0.0001632665642333581</v>
       </c>
       <c r="CG6" t="n">
         <v>0.3371997267952399</v>
@@ -3777,10 +3777,10 @@
         <v>0.001731028734893375</v>
       </c>
       <c r="BY7" t="n">
+        <v>0.0001915159989126558</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>0.0002063132762136322</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0.0001915159989126558</v>
       </c>
       <c r="CA7" t="n">
         <v>0.01558353043301856</v>
@@ -3930,7 +3930,7 @@
         <v>0.00108653723588712</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.004525958277638731</v>
+        <v>0.004540363348223581</v>
       </c>
       <c r="DY7" t="n">
         <v>0.00444465012355223</v>
